--- a/XLSX/Ball.xlsx
+++ b/XLSX/Ball.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\dodge-ball-raylib\XLSX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\dodge-ball\XLSX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09C65B3-6475-472B-AAEE-456567C82F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CAE7A0-6346-4BCE-A568-9416D364AAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>Num</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -55,6 +55,19 @@
   </si>
   <si>
     <t>1.0,0.0,1.0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0,1.0,1.0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0,1.0,1.0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0,0.0,0.0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -418,8 +431,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="18.796875" customWidth="1"/>
+    <col min="2" max="2" width="19.296875" customWidth="1"/>
+    <col min="3" max="3" width="20.59765625" customWidth="1"/>
+    <col min="4" max="4" width="14.19921875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
@@ -457,7 +476,7 @@
         <v>100</v>
       </c>
       <c r="C3" s="1">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>6</v>
@@ -471,10 +490,52 @@
         <v>200</v>
       </c>
       <c r="C4" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>1003</v>
+      </c>
+      <c r="B5">
+        <v>300</v>
+      </c>
+      <c r="C5">
+        <v>200</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>1004</v>
+      </c>
+      <c r="B6">
+        <v>400</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>1005</v>
+      </c>
+      <c r="B7">
+        <v>500</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/XLSX/Ball.xlsx
+++ b/XLSX/Ball.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\dodge-ball\XLSX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E701C93-970C-403C-AB09-BF5DF53E96D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70AB4FF-4467-48CC-A3E3-507B1BB78447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -476,7 +476,7 @@
         <v>100</v>
       </c>
       <c r="C3" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>6</v>
@@ -490,7 +490,7 @@
         <v>200</v>
       </c>
       <c r="C4" s="1">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
@@ -504,7 +504,7 @@
         <v>300</v>
       </c>
       <c r="C5">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>8</v>
@@ -518,7 +518,7 @@
         <v>400</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>9</v>
@@ -532,7 +532,7 @@
         <v>500</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>10</v>

--- a/XLSX/Ball.xlsx
+++ b/XLSX/Ball.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\dodge-ball\XLSX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70AB4FF-4467-48CC-A3E3-507B1BB78447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6DDC67-2D7B-46A5-A827-D034AC898BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,61 +25,73 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="12">
   <si>
     <t>Num</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Speed</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Size</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Color</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>float[]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>1.0,1.0,0.0</t>
   </si>
   <si>
     <t>1.0,0.0,1.0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>0.0,1.0,1.0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>1.0,1.0,1.0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>0.0,0.0,0.0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.0,1.0,0.0</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -106,7 +118,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -123,6 +135,36 @@
         <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -133,24 +175,58 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="3" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="5" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="4" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="7" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="6" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="8">
+    <cellStyle name="20% - 강조색1" xfId="3" builtinId="30"/>
+    <cellStyle name="20% - 강조색2" xfId="5" builtinId="34"/>
+    <cellStyle name="20% - 강조색5" xfId="7" builtinId="46"/>
+    <cellStyle name="40% - 강조색1" xfId="4" builtinId="31"/>
+    <cellStyle name="40% - 강조색4" xfId="6" builtinId="43"/>
     <cellStyle name="보통" xfId="2" builtinId="28"/>
     <cellStyle name="좋음" xfId="1" builtinId="26"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -431,115 +507,395 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.796875" customWidth="1"/>
     <col min="2" max="2" width="19.296875" customWidth="1"/>
-    <col min="3" max="3" width="20.59765625" customWidth="1"/>
-    <col min="4" max="4" width="14.19921875" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="17.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A3" s="1">
+    <row r="3" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="5">
         <v>1001</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="5">
         <v>100</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="5">
         <v>60</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="5">
+        <v>1002</v>
+      </c>
+      <c r="B4" s="5">
+        <v>200</v>
+      </c>
+      <c r="C4" s="5">
+        <v>50</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A4" s="1">
-        <v>1002</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="5" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
+        <v>1003</v>
+      </c>
+      <c r="B5" s="5">
+        <v>300</v>
+      </c>
+      <c r="C5" s="5">
+        <v>40</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="5">
+        <v>1004</v>
+      </c>
+      <c r="B6" s="5">
+        <v>400</v>
+      </c>
+      <c r="C6" s="5">
+        <v>30</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="5">
+        <v>1005</v>
+      </c>
+      <c r="B7" s="5">
+        <v>500</v>
+      </c>
+      <c r="C7" s="5">
+        <v>20</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
+        <v>2001</v>
+      </c>
+      <c r="B8" s="3">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3">
+        <v>60</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
+        <v>2002</v>
+      </c>
+      <c r="B9" s="3">
         <v>200</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C9" s="3">
         <v>50</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A5">
-        <v>1003</v>
-      </c>
-      <c r="B5">
+    <row r="10" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4">
+        <v>2003</v>
+      </c>
+      <c r="B10" s="4">
         <v>300</v>
       </c>
-      <c r="C5">
+      <c r="C10" s="4">
         <v>40</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="4">
+        <v>2004</v>
+      </c>
+      <c r="B11" s="4">
+        <v>400</v>
+      </c>
+      <c r="C11" s="4">
+        <v>30</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="4">
+        <v>2005</v>
+      </c>
+      <c r="B12" s="4">
+        <v>500</v>
+      </c>
+      <c r="C12" s="4">
+        <v>20</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="6">
+        <v>3001</v>
+      </c>
+      <c r="B13" s="6">
+        <v>100</v>
+      </c>
+      <c r="C13" s="6">
+        <v>60</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A6">
-        <v>1004</v>
-      </c>
-      <c r="B6">
+    <row r="14" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="6">
+        <v>3002</v>
+      </c>
+      <c r="B14" s="6">
+        <v>200</v>
+      </c>
+      <c r="C14" s="6">
+        <v>50</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="6">
+        <v>3003</v>
+      </c>
+      <c r="B15" s="7">
+        <v>300</v>
+      </c>
+      <c r="C15" s="7">
+        <v>40</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="6">
+        <v>3004</v>
+      </c>
+      <c r="B16" s="7">
         <v>400</v>
       </c>
-      <c r="C6">
+      <c r="C16" s="7">
         <v>30</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D16" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="6">
+        <v>3005</v>
+      </c>
+      <c r="B17" s="7">
+        <v>500</v>
+      </c>
+      <c r="C17" s="7">
+        <v>20</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="8">
+        <v>4001</v>
+      </c>
+      <c r="B18" s="8">
+        <v>100</v>
+      </c>
+      <c r="C18" s="8">
+        <v>60</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A7">
-        <v>1005</v>
-      </c>
-      <c r="B7">
+    <row r="19" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="8">
+        <v>4002</v>
+      </c>
+      <c r="B19" s="8">
+        <v>200</v>
+      </c>
+      <c r="C19" s="8">
+        <v>50</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="8">
+        <v>4003</v>
+      </c>
+      <c r="B20" s="9">
+        <v>300</v>
+      </c>
+      <c r="C20" s="9">
+        <v>40</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="8">
+        <v>4004</v>
+      </c>
+      <c r="B21" s="9">
+        <v>400</v>
+      </c>
+      <c r="C21" s="9">
+        <v>30</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="8">
+        <v>4005</v>
+      </c>
+      <c r="B22" s="9">
         <v>500</v>
       </c>
-      <c r="C7">
+      <c r="C22" s="9">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D22" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="10">
+        <v>5001</v>
+      </c>
+      <c r="B23" s="10">
+        <v>100</v>
+      </c>
+      <c r="C23" s="10">
+        <v>60</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="24" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="10">
+        <v>5002</v>
+      </c>
+      <c r="B24" s="10">
+        <v>200</v>
+      </c>
+      <c r="C24" s="10">
+        <v>50</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="10">
+        <v>5003</v>
+      </c>
+      <c r="B25" s="11">
+        <v>300</v>
+      </c>
+      <c r="C25" s="11">
+        <v>40</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="10">
+        <v>5004</v>
+      </c>
+      <c r="B26" s="11">
+        <v>400</v>
+      </c>
+      <c r="C26" s="11">
+        <v>30</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="10">
+        <v>5005</v>
+      </c>
+      <c r="B27" s="11">
+        <v>500</v>
+      </c>
+      <c r="C27" s="11">
+        <v>20</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>